--- a/docs/代码体检报告.xlsx
+++ b/docs/代码体检报告.xlsx
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>19/19</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>826/826</t>
+          <t>827/827</t>
         </is>
       </c>
       <c r="C165" t="n">

--- a/docs/代码体检报告.xlsx
+++ b/docs/代码体检报告.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>21/22</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -509,27 +509,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>src/common/AppConfig.cpp</t>
+          <t>src/comm/CommTypes.h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>src/common/AppConfig.h</t>
+          <t>src/comm/EdgeLink.cpp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -539,7 +539,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>src/common/Constants.h</t>
+          <t>src/comm/EdgeLink.h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -554,12 +554,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>src/common/DatabaseManager.cpp</t>
+          <t>src/comm/EdgeService.cpp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -569,7 +569,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>src/common/DatabaseManager.h</t>
+          <t>src/comm/EdgeService.h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -584,12 +584,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>src/common/Logger.cpp</t>
+          <t>src/common/AppConfig.cpp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>44/44</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -599,7 +599,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>src/common/Logger.h</t>
+          <t>src/common/AppConfig.h</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>src/common/PositionFormatter.h</t>
+          <t>src/common/Constants.h</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>src/components/BaseDialog.cpp</t>
+          <t>src/common/DatabaseManager.cpp</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -644,7 +644,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>src/components/BaseDialog.h</t>
+          <t>src/common/DatabaseManager.h</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -659,12 +659,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>src/components/CameraCapture.cpp</t>
+          <t>src/common/Logger.cpp</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>src/components/CameraCapture.h</t>
+          <t>src/common/Logger.h</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -689,12 +689,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>src/components/DeepFaceExtractor.cpp</t>
+          <t>src/common/PositionFormatter.h</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -704,7 +704,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>src/components/DeepFaceExtractor.h</t>
+          <t>src/common/UserInputValidator.h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -719,12 +719,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>src/components/DrawerOpeningDialog.cpp</t>
+          <t>src/components/BaseDialog.cpp</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -734,7 +734,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>src/components/DrawerOpeningDialog.h</t>
+          <t>src/components/BaseDialog.h</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -749,12 +749,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>src/components/FaceCameraWidget.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28/28</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -764,7 +764,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>src/components/FaceCameraWidget.h</t>
+          <t>src/components/CameraCapture.h</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>src/components/FlowDialogs.cpp</t>
+          <t>src/components/DeepFaceExtractor.cpp</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -794,7 +794,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>src/components/FlowDialogs.h</t>
+          <t>src/components/DeepFaceExtractor.h</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>src/components/FormFactory.h</t>
+          <t>src/components/DrawerOpeningDialog.cpp</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -824,12 +824,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>src/components/MessageDialog.cpp</t>
+          <t>src/components/DrawerOpeningDialog.h</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -839,12 +839,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>src/components/MessageDialog.h</t>
+          <t>src/components/FaceCameraWidget.cpp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>28/28</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -854,12 +854,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>src/components/MultiSelectFilter.cpp</t>
+          <t>src/components/FaceCameraWidget.h</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -869,12 +869,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>src/components/MultiSelectFilter.h</t>
+          <t>src/components/FlowDialogs.cpp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -884,12 +884,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>src/components/NumKeypad.cpp</t>
+          <t>src/components/FlowDialogs.h</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -899,7 +899,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>src/components/NumKeypad.h</t>
+          <t>src/components/FormFactory.h</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -914,12 +914,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>src/components/PaginationBar.cpp</t>
+          <t>src/components/MessageDialog.cpp</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -929,7 +929,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>src/components/PaginationBar.h</t>
+          <t>src/components/MessageDialog.h</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>src/components/ResultDialog.cpp</t>
+          <t>src/components/MultiSelectFilter.cpp</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -959,7 +959,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>src/components/ResultDialog.h</t>
+          <t>src/components/MultiSelectFilter.h</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -974,12 +974,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>src/components/SearchBar.cpp</t>
+          <t>src/components/NumKeypad.cpp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>19/19</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -989,7 +989,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>src/components/SearchBar.h</t>
+          <t>src/components/NumKeypad.h</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1004,12 +1004,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>src/components/SidebarMenu.cpp</t>
+          <t>src/components/PaginationBar.cpp</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1019,7 +1019,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>src/components/SidebarMenu.h</t>
+          <t>src/components/PaginationBar.h</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1034,12 +1034,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>src/components/SingleSelectFilter.cpp</t>
+          <t>src/components/ResultDialog.cpp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1049,7 +1049,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>src/components/SingleSelectFilter.h</t>
+          <t>src/components/ResultDialog.h</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1064,12 +1064,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.cpp</t>
+          <t>src/components/SearchBar.cpp</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1079,7 +1079,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.h</t>
+          <t>src/components/SearchBar.h</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>src/components/TopBar.cpp</t>
+          <t>src/components/SingleSelectFilter.cpp</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1109,7 +1109,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>src/components/TopBar.h</t>
+          <t>src/components/SingleSelectFilter.h</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.cpp</t>
+          <t>src/components/SoftKeyboard.cpp</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1139,7 +1139,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.h</t>
+          <t>src/components/SoftKeyboard.h</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>src/controller/AlertController.cpp</t>
+          <t>src/components/TopBar.cpp</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>src/controller/AlertController.h</t>
+          <t>src/components/TopBar.h</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1184,12 +1184,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.cpp</t>
+          <t>src/components/VerifyAlertDialog.cpp</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1199,7 +1199,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.h</t>
+          <t>src/components/VerifyAlertDialog.h</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.cpp</t>
+          <t>src/controller/AlertController.cpp</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1229,7 +1229,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.h</t>
+          <t>src/controller/AlertController.h</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1244,12 +1244,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.cpp</t>
+          <t>src/controller/AuthController.cpp</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1259,7 +1259,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.h</t>
+          <t>src/controller/AuthController.h</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>src/controller/UserController.cpp</t>
+          <t>src/controller/SettingController.cpp</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1289,7 +1289,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>src/controller/UserController.h</t>
+          <t>src/controller/SettingController.h</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.cpp</t>
+          <t>src/controller/ToolController.cpp</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21/21</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1319,7 +1319,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.h</t>
+          <t>src/controller/ToolController.h</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1334,12 +1334,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>src/db/BaseDAO.h</t>
+          <t>src/controller/UserController.cpp</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1349,12 +1349,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.cpp</t>
+          <t>src/controller/UserController.h</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1364,12 +1364,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.h</t>
+          <t>src/db/AlertDAO.cpp</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1379,12 +1379,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.cpp</t>
+          <t>src/db/AlertDAO.h</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1394,7 +1394,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.h</t>
+          <t>src/db/BaseDAO.h</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1409,12 +1409,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.cpp</t>
+          <t>src/db/ConfigDAO.cpp</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1424,7 +1424,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.h</t>
+          <t>src/db/ConfigDAO.h</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.cpp</t>
+          <t>src/db/DepartmentDAO.cpp</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1454,7 +1454,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.h</t>
+          <t>src/db/DepartmentDAO.h</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1469,12 +1469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.cpp</t>
+          <t>src/db/FaceRecogLogDAO.cpp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1484,7 +1484,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.h</t>
+          <t>src/db/FaceRecogLogDAO.h</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOCategory.cpp</t>
+          <t>src/db/RecordDAO.cpp</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1514,12 +1514,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMachineGroup.cpp</t>
+          <t>src/db/RecordDAO.h</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1529,12 +1529,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMaintenance.cpp</t>
+          <t>src/db/TaskTypeDAO.cpp</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1544,12 +1544,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMapping.cpp</t>
+          <t>src/db/TaskTypeDAO.h</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1559,12 +1559,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOPosition.cpp</t>
+          <t>src/db/ToolDAO.cpp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1574,12 +1574,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOToolEntity.cpp</t>
+          <t>src/db/ToolDAO.h</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1589,12 +1589,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.cpp</t>
+          <t>src/db/ToolDAOCategory.cpp</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26/26</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1604,12 +1604,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.h</t>
+          <t>src/db/ToolDAOMachineGroup.cpp</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1619,12 +1619,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>src/model/AlertLog.h</t>
+          <t>src/db/ToolDAOMaintenance.cpp</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1634,12 +1634,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>src/model/BorrowRecord.h</t>
+          <t>src/db/ToolDAOMapping.cpp</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1649,12 +1649,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>src/model/Department.h</t>
+          <t>src/db/ToolDAOPosition.cpp</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1664,12 +1664,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>src/model/MachineGroup.h</t>
+          <t>src/db/ToolDAOToolEntity.cpp</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1679,12 +1679,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>src/model/ReturnRecord.h</t>
+          <t>src/db/UserDAO.cpp</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>27/27</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1694,7 +1694,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>src/model/TaskType.h</t>
+          <t>src/db/UserDAO.h</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>src/model/ToolCabinet.h</t>
+          <t>src/model/AlertLog.h</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>src/model/ToolCategory.h</t>
+          <t>src/model/BorrowRecord.h</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>src/model/ToolInfo.h</t>
+          <t>src/model/ReturnRecord.h</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>src/model/User.h</t>
+          <t>src/model/TaskType.h</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.cpp</t>
+          <t>src/model/ToolCabinet.h</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1784,7 +1784,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.h</t>
+          <t>src/model/ToolCategory.h</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.ui</t>
+          <t>src/model/ToolInfo.h</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1808,18 +1808,18 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.cpp</t>
+          <t>src/model/User.h</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1829,12 +1829,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.h</t>
+          <t>src/pages/AlertLogsPage.cpp</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1844,12 +1844,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.cpp</t>
+          <t>src/pages/AlertLogsPage.h</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1859,7 +1859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.h</t>
+          <t>src/pages/AlertLogsPage.ui</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1868,18 +1868,18 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>src/pages/DashboardPage.cpp</t>
+          <t>src/pages/BatchImportDialog.cpp</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>25/25</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1889,7 +1889,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>src/pages/DashboardPage.h</t>
+          <t>src/pages/BatchImportDialog.h</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1904,12 +1904,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.cpp</t>
+          <t>src/pages/CabinetSessionDialog.cpp</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1919,7 +1919,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.h</t>
+          <t>src/pages/CabinetSessionDialog.h</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1934,27 +1934,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.ui</t>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.cpp</t>
+          <t>src/pages/ForceChangePasswordDialog.h</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1964,12 +1964,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.h</t>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/12</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1979,12 +1979,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageFace.cpp</t>
+          <t>src/pages/ForgotPasswordDialog.h</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1994,12 +1994,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageUI.cpp</t>
+          <t>src/pages/HelpManualDialog.cpp</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2009,12 +2009,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.cpp</t>
+          <t>src/pages/HelpManualDialog.h</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2024,12 +2024,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.h</t>
+          <t>src/pages/LedgerStatsPage.cpp</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2039,7 +2039,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.ui</t>
+          <t>src/pages/LedgerStatsPage.h</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2048,33 +2048,33 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.cpp</t>
+          <t>src/pages/LedgerStatsPage.ui</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>27/27</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.h</t>
+          <t>src/pages/LoginPage.cpp</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2084,12 +2084,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageBackup.cpp</t>
+          <t>src/pages/LoginPage.h</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2099,12 +2099,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
+          <t>src/pages/LoginPageFace.cpp</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2114,12 +2114,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
+          <t>src/pages/LoginPageUI.cpp</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2129,12 +2129,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPagePanels.cpp</t>
+          <t>src/pages/MenuHomePage.cpp</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2144,12 +2144,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageSystemInfo.cpp</t>
+          <t>src/pages/MenuHomePage.h</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2159,12 +2159,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.cpp</t>
+          <t>src/pages/RoleSelectDialog.cpp</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2174,7 +2174,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.h</t>
+          <t>src/pages/RoleSelectDialog.h</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2189,27 +2189,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.ui</t>
+          <t>src/pages/SystemMaintenancePage.cpp</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>25/25</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPageFlow.cpp</t>
+          <t>src/pages/SystemMaintenancePage.h</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2219,27 +2219,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.cpp</t>
+          <t>src/pages/SystemMaintenancePage.ui</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.h</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>21/22</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2249,7 +2249,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.ui</t>
+          <t>src/pages/SystemSettingsPage.h</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2258,18 +2258,18 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPageDialog.cpp</t>
+          <t>src/pages/SystemSettingsPageBackup.cpp</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2279,12 +2279,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.cpp</t>
+          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2294,12 +2294,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.h</t>
+          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2309,27 +2309,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.ui</t>
+          <t>src/pages/SystemSettingsPagePanels.cpp</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPageDialog.cpp</t>
+          <t>src/pages/ToolBorrowPage.cpp</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2339,12 +2339,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.cpp</t>
+          <t>src/pages/ToolBorrowPage.h</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2354,7 +2354,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.h</t>
+          <t>src/pages/ToolBorrowPage.ui</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2363,33 +2363,33 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.ui</t>
+          <t>src/pages/ToolBorrowPageFlow.cpp</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDetail.cpp</t>
+          <t>src/pages/ToolCheckinPage.cpp</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2399,12 +2399,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDocument.cpp</t>
+          <t>src/pages/ToolCheckinPage.h</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2414,27 +2414,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageToolForm.cpp</t>
+          <t>src/pages/ToolCheckinPage.ui</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.cpp</t>
+          <t>src/pages/ToolCheckinPageDialog.cpp</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2444,12 +2444,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.h</t>
+          <t>src/pages/ToolCheckoutPage.cpp</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>17/17</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2459,7 +2459,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.ui</t>
+          <t>src/pages/ToolCheckoutPage.h</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2468,33 +2468,33 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>src/pages/UserEntryDialog.cpp</t>
+          <t>src/pages/ToolCheckoutPage.ui</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>src/pages/UserEntryDialog.h</t>
+          <t>src/pages/ToolCheckoutPageDialog.cpp</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2504,27 +2504,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>src/pages/UserEntryDialog.ui</t>
+          <t>src/pages/ToolManagementPage.cpp</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.cpp</t>
+          <t>src/pages/ToolManagementPage.h</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2534,7 +2534,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.h</t>
+          <t>src/pages/ToolManagementPage.ui</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2543,33 +2543,33 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.ui</t>
+          <t>src/pages/ToolManagementPageDetail.cpp</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
+          <t>src/pages/ToolManagementPageDocument.cpp</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2579,12 +2579,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageUserDialog.cpp</t>
+          <t>src/pages/ToolManagementPageToolForm.cpp</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2594,12 +2594,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>src/services/AlertService.cpp</t>
+          <t>src/pages/ToolReturnPage.cpp</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2609,7 +2609,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>src/services/AlertService.h</t>
+          <t>src/pages/ToolReturnPage.h</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2624,27 +2624,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>src/services/AuthService.cpp</t>
+          <t>src/pages/ToolReturnPage.ui</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>src/services/AuthService.h</t>
+          <t>src/pages/UserManagementPage.cpp</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2654,12 +2654,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.cpp</t>
+          <t>src/pages/UserManagementPage.h</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2669,7 +2669,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.h</t>
+          <t>src/pages/UserManagementPage.ui</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2678,18 +2678,18 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.cpp</t>
+          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2699,12 +2699,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.h</t>
+          <t>src/pages/UserManagementPageUserDialog.cpp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2714,12 +2714,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.cpp</t>
+          <t>src/services/AlertService.cpp</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2729,7 +2729,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.h</t>
+          <t>src/services/AlertService.h</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.cpp</t>
+          <t>src/services/AuthService.cpp</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2759,7 +2759,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.h</t>
+          <t>src/services/AuthService.h</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2774,12 +2774,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.cpp</t>
+          <t>src/services/BorrowService.cpp</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2789,7 +2789,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.h</t>
+          <t>src/services/BorrowService.h</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2804,12 +2804,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>src/services/SettingService.cpp</t>
+          <t>src/services/CheckoutService.cpp</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2819,7 +2819,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>src/services/SettingService.h</t>
+          <t>src/services/CheckoutService.h</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>src/services/ToolService.cpp</t>
+          <t>src/services/FaceRecognitionService.cpp</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2849,7 +2849,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>src/services/ToolService.h</t>
+          <t>src/services/FaceRecognitionService.h</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2864,12 +2864,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>src/utils/StyleHelper.cpp</t>
+          <t>src/services/MaintenanceService.cpp</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2879,31 +2879,151 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>src/services/MaintenanceService.h</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>src/services/ReturnService.cpp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>src/services/ReturnService.h</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>src/services/SettingService.cpp</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>src/services/SettingService.h</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>src/services/ToolService.cpp</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>src/services/ToolService.h</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>src/utils/StyleHelper.cpp</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>src/utils/StyleHelper.h</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>827/827</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>10</v>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>808/833</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2917,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2939,6 +3059,381 @@
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>src/MainWindow.cpp</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>857</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>navigateToPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeService.cpp</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>currentMSecsSinceEpoch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>src/db/ConfigDAO.cpp</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>loadAll</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>src/db/ConfigDAO.cpp</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>saveBatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>src/db/ConfigDAO.cpp</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>src/pages/BatchImportDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>254</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>onDownloadTemplate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>setupContent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>buildPasswordRow</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>149</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>openKeypad</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>157</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>onSubmit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>205</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>onExitLogin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>setupContent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>67</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>buildVerifyPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>106</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>buildResetPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>155</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>buildPasswordRow</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>198</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>openKeypad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>showEvent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>212</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hideEvent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>218</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>onPollFace</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>224</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>verifyOnce</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>268</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gotoResetPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>279</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>onResetSubmit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>318</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>onCancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>src/pages/RoleSelectDialog.cpp</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>41</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>setupContent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>src/pages/SystemSettingsPage.cpp</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>330</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>refresh</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3014,6 +3509,102 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>src/comm/CommTypes.h</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeLink.cpp</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>185</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeLink.h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeService.cpp</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>361</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeService.h</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>104</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>src/common/UserInputValidator.h</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>79</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>文件末尾缺换行</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/代码体检报告.xlsx
+++ b/docs/代码体检报告.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C173"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>44/46</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>src/common/Logger.cpp</t>
+          <t>src/common/DiskSpaceGuard.cpp</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>src/common/Logger.h</t>
+          <t>src/common/DiskSpaceGuard.h</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>src/common/PositionFormatter.h</t>
+          <t>src/common/Logger.cpp</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>src/common/UserInputValidator.h</t>
+          <t>src/common/Logger.h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -719,12 +719,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>src/components/BaseDialog.cpp</t>
+          <t>src/common/PositionFormatter.h</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -734,7 +734,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>src/components/BaseDialog.h</t>
+          <t>src/common/UserInputValidator.h</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -749,12 +749,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>src/components/CameraCapture.cpp</t>
+          <t>src/components/BaseDialog.cpp</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -764,7 +764,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>src/components/CameraCapture.h</t>
+          <t>src/components/BaseDialog.h</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>src/components/DeepFaceExtractor.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -794,7 +794,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>src/components/DeepFaceExtractor.h</t>
+          <t>src/components/CameraCapture.h</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>src/components/DrawerOpeningDialog.cpp</t>
+          <t>src/components/DeepFaceExtractor.cpp</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -824,7 +824,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>src/components/DrawerOpeningDialog.h</t>
+          <t>src/components/DeepFaceExtractor.h</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>src/components/FaceCameraWidget.cpp</t>
+          <t>src/components/DrawerOpeningDialog.cpp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28/28</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -854,7 +854,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>src/components/FaceCameraWidget.h</t>
+          <t>src/components/DrawerOpeningDialog.h</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -869,12 +869,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>src/components/FlowDialogs.cpp</t>
+          <t>src/components/FaceCameraWidget.cpp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>28/28</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -884,7 +884,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>src/components/FlowDialogs.h</t>
+          <t>src/components/FaceCameraWidget.h</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>src/components/FormFactory.h</t>
+          <t>src/components/FlowDialogs.cpp</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -914,12 +914,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>src/components/MessageDialog.cpp</t>
+          <t>src/components/FlowDialogs.h</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -929,7 +929,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>src/components/MessageDialog.h</t>
+          <t>src/components/FormFactory.h</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>src/components/MultiSelectFilter.cpp</t>
+          <t>src/components/MessageDialog.cpp</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -959,7 +959,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>src/components/MultiSelectFilter.h</t>
+          <t>src/components/MessageDialog.h</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -974,12 +974,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>src/components/NumKeypad.cpp</t>
+          <t>src/components/MultiSelectFilter.cpp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -989,7 +989,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>src/components/NumKeypad.h</t>
+          <t>src/components/MultiSelectFilter.h</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1004,12 +1004,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>src/components/PaginationBar.cpp</t>
+          <t>src/components/NumKeypad.cpp</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>19/19</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1019,7 +1019,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>src/components/PaginationBar.h</t>
+          <t>src/components/NumKeypad.h</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1034,12 +1034,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>src/components/ResultDialog.cpp</t>
+          <t>src/components/PaginationBar.cpp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1049,7 +1049,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>src/components/ResultDialog.h</t>
+          <t>src/components/PaginationBar.h</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1064,12 +1064,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>src/components/SearchBar.cpp</t>
+          <t>src/components/ResultDialog.cpp</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1079,7 +1079,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>src/components/SearchBar.h</t>
+          <t>src/components/ResultDialog.h</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>src/components/SingleSelectFilter.cpp</t>
+          <t>src/components/SearchBar.cpp</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1109,7 +1109,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>src/components/SingleSelectFilter.h</t>
+          <t>src/components/SearchBar.h</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.cpp</t>
+          <t>src/components/SingleSelectFilter.cpp</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1139,7 +1139,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.h</t>
+          <t>src/components/SingleSelectFilter.h</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1154,42 +1154,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>src/components/TopBar.cpp</t>
+          <t>src/components/SoftKeyboard.cpp</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>int v =</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>src/components/TopBar.h</t>
+          <t>src/components/SoftKeyboard.cpp</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>23/23</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.cpp</t>
+          <t>src/components/SoftKeyboard.h</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1199,12 +1199,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.h</t>
+          <t>src/components/TopBar.cpp</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1214,12 +1214,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>src/controller/AlertController.cpp</t>
+          <t>src/components/TopBar.h</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1229,12 +1229,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>src/controller/AlertController.h</t>
+          <t>src/components/VerifyAlertDialog.cpp</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1244,12 +1244,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.cpp</t>
+          <t>src/components/VerifyAlertDialog.h</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1259,12 +1259,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.h</t>
+          <t>src/controller/AuthController.cpp</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1274,12 +1274,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.cpp</t>
+          <t>src/controller/AuthController.h</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1289,12 +1289,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.h</t>
+          <t>src/controller/SettingController.cpp</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1304,12 +1304,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.cpp</t>
+          <t>src/controller/SettingController.h</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1319,12 +1319,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.h</t>
+          <t>src/controller/ToolController.cpp</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1334,12 +1334,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>src/controller/UserController.cpp</t>
+          <t>src/controller/ToolController.h</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1349,12 +1349,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>src/controller/UserController.h</t>
+          <t>src/controller/UserController.cpp</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1364,12 +1364,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.cpp</t>
+          <t>src/controller/UserController.h</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1379,12 +1379,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.h</t>
+          <t>src/db/AlertDAO.cpp</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1394,7 +1394,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>src/db/BaseDAO.h</t>
+          <t>src/db/AlertDAO.h</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1409,12 +1409,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/db/BaseDAO.h</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1424,12 +1424,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.h</t>
+          <t>src/db/ConfigDAO.cpp</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1439,12 +1439,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.cpp</t>
+          <t>src/db/ConfigDAO.h</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1454,12 +1454,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.h</t>
+          <t>src/db/DepartmentDAO.cpp</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1469,12 +1469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.cpp</t>
+          <t>src/db/DepartmentDAO.h</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1484,12 +1484,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.h</t>
+          <t>src/db/FaceRecogLogDAO.cpp</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1499,12 +1499,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.cpp</t>
+          <t>src/db/FaceRecogLogDAO.h</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1514,12 +1514,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.h</t>
+          <t>src/db/RecordDAO.cpp</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1529,12 +1529,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.cpp</t>
+          <t>src/db/RecordDAO.h</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1544,12 +1544,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.h</t>
+          <t>src/db/TaskTypeDAO.cpp</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1559,12 +1559,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.cpp</t>
+          <t>src/db/TaskTypeDAO.h</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1574,12 +1574,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.h</t>
+          <t>src/db/ToolDAO.cpp</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1589,12 +1589,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOCategory.cpp</t>
+          <t>src/db/ToolDAO.h</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1604,12 +1604,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMachineGroup.cpp</t>
+          <t>src/db/ToolDAOCategory.cpp</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1619,12 +1619,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMaintenance.cpp</t>
+          <t>src/db/ToolDAOMachineGroup.cpp</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1634,12 +1634,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMapping.cpp</t>
+          <t>src/db/ToolDAOMaintenance.cpp</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1649,12 +1649,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOPosition.cpp</t>
+          <t>src/db/ToolDAOMapping.cpp</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1664,12 +1664,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOToolEntity.cpp</t>
+          <t>src/db/ToolDAOPosition.cpp</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1679,12 +1679,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.cpp</t>
+          <t>src/db/ToolDAOToolEntity.cpp</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>27/27</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1694,12 +1694,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.h</t>
+          <t>src/db/UserDAO.cpp</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>27/27</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1709,7 +1709,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>src/model/AlertLog.h</t>
+          <t>src/db/UserDAO.h</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>src/model/BorrowRecord.h</t>
+          <t>src/model/AlertLog.h</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>src/model/ReturnRecord.h</t>
+          <t>src/model/BorrowRecord.h</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>src/model/TaskType.h</t>
+          <t>src/model/ReturnRecord.h</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>src/model/ToolCabinet.h</t>
+          <t>src/model/TaskType.h</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>src/model/ToolCategory.h</t>
+          <t>src/model/ToolCabinet.h</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>src/model/ToolInfo.h</t>
+          <t>src/model/ToolCategory.h</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1814,7 +1814,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>src/model/User.h</t>
+          <t>src/model/ToolInfo.h</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1829,12 +1829,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.cpp</t>
+          <t>src/model/User.h</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1844,12 +1844,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.h</t>
+          <t>src/pages/AlertLogsPage.cpp</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1859,7 +1859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.ui</t>
+          <t>src/pages/AlertLogsPage.h</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1868,33 +1868,33 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.cpp</t>
+          <t>src/pages/AlertLogsPage.ui</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.h</t>
+          <t>src/pages/BatchImportDialog.cpp</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1904,12 +1904,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.cpp</t>
+          <t>src/pages/BatchImportDialog.h</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1919,12 +1919,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.h</t>
+          <t>src/pages/CabinetSessionDialog.cpp</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1934,12 +1934,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/CabinetSessionDialog.h</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1949,12 +1949,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.h</t>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1964,12 +1964,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/pages/ForceChangePasswordDialog.h</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1979,12 +1979,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.h</t>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1994,12 +1994,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>src/pages/HelpManualDialog.cpp</t>
+          <t>src/pages/ForgotPasswordDialog.h</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2009,12 +2009,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>src/pages/HelpManualDialog.h</t>
+          <t>src/pages/HelpManualDialog.cpp</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2024,12 +2024,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.cpp</t>
+          <t>src/pages/HelpManualDialog.h</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2039,12 +2039,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.h</t>
+          <t>src/pages/LedgerStatsPage.cpp</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/13</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2054,7 +2054,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.ui</t>
+          <t>src/pages/LedgerStatsPage.h</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2063,33 +2063,33 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.cpp</t>
+          <t>src/pages/LedgerStatsPage.ui</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.h</t>
+          <t>src/pages/LoginPage.cpp</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2099,12 +2099,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageFace.cpp</t>
+          <t>src/pages/LoginPage.h</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2114,12 +2114,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageUI.cpp</t>
+          <t>src/pages/LoginPageFace.cpp</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2129,12 +2129,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>src/pages/MenuHomePage.cpp</t>
+          <t>src/pages/LoginPageUI.cpp</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2144,12 +2144,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>src/pages/MenuHomePage.h</t>
+          <t>src/pages/MenuHomePage.cpp</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2159,12 +2159,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.cpp</t>
+          <t>src/pages/MenuHomePage.h</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2174,12 +2174,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.h</t>
+          <t>src/pages/RoleSelectDialog.cpp</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2189,12 +2189,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.cpp</t>
+          <t>src/pages/RoleSelectDialog.h</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>25/25</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2204,12 +2204,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.h</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>21/22</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2219,7 +2219,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>src/pages/SystemMaintenancePage.ui</t>
+          <t>src/pages/SystemSettingsPage.h</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2228,18 +2228,18 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.cpp</t>
+          <t>src/pages/SystemSettingsPageBackup.cpp</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21/22</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2249,12 +2249,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.h</t>
+          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2264,7 +2264,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageBackup.cpp</t>
+          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
+          <t>src/pages/SystemSettingsPagePanels.cpp</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
+          <t>src/pages/SystemSettingsPageTaskConfig.cpp</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2309,12 +2309,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPagePanels.cpp</t>
+          <t>src/pages/ToolBorrowPage.cpp</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2324,12 +2324,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.cpp</t>
+          <t>src/pages/ToolBorrowPage.h</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2339,7 +2339,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.h</t>
+          <t>src/pages/ToolBorrowPage.ui</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2348,33 +2348,33 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.ui</t>
+          <t>src/pages/ToolBorrowPageFlow.cpp</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPageFlow.cpp</t>
+          <t>src/pages/ToolCheckinPage.cpp</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2384,12 +2384,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.cpp</t>
+          <t>src/pages/ToolCheckinPage.h</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2399,7 +2399,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.h</t>
+          <t>src/pages/ToolCheckinPage.ui</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2408,33 +2408,33 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.ui</t>
+          <t>src/pages/ToolCheckinPageDialog.cpp</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPageDialog.cpp</t>
+          <t>src/pages/ToolListDialog.cpp</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2444,12 +2444,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.cpp</t>
+          <t>src/pages/ToolListDialog.h</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2459,12 +2459,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.h</t>
+          <t>src/pages/ToolManagementPage.cpp</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2474,7 +2474,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPage.ui</t>
+          <t>src/pages/ToolManagementPage.h</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2483,33 +2483,33 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckoutPageDialog.cpp</t>
+          <t>src/pages/ToolManagementPage.ui</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.cpp</t>
+          <t>src/pages/ToolManagementPageDetail.cpp</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2519,12 +2519,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.h</t>
+          <t>src/pages/ToolManagementPageDocument.cpp</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2534,27 +2534,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.ui</t>
+          <t>src/pages/ToolManagementPageToolForm.cpp</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDetail.cpp</t>
+          <t>src/pages/ToolReturnPage.cpp</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>14/14</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2564,12 +2564,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDocument.cpp</t>
+          <t>src/pages/ToolReturnPage.h</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2579,22 +2579,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageToolForm.cpp</t>
+          <t>src/pages/ToolReturnPage.ui</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.cpp</t>
+          <t>src/pages/UserManagementPage.cpp</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.h</t>
+          <t>src/pages/UserManagementPage.h</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2624,7 +2624,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.ui</t>
+          <t>src/pages/UserManagementPage.ui</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.cpp</t>
+          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2654,12 +2654,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.h</t>
+          <t>src/pages/UserManagementPageUserDialog.cpp</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2669,27 +2669,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.ui</t>
+          <t>src/services/AlertService.cpp</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
+          <t>src/services/AlertService.h</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2699,12 +2699,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageUserDialog.cpp</t>
+          <t>src/services/AuthService.cpp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2714,12 +2714,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>src/services/AlertService.cpp</t>
+          <t>src/services/AuthService.h</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2729,12 +2729,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>src/services/AlertService.h</t>
+          <t>src/services/BorrowService.cpp</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2744,12 +2744,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>src/services/AuthService.cpp</t>
+          <t>src/services/BorrowService.h</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2759,12 +2759,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>src/services/AuthService.h</t>
+          <t>src/services/CheckoutService.cpp</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2774,12 +2774,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.cpp</t>
+          <t>src/services/CheckoutService.h</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2789,12 +2789,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.h</t>
+          <t>src/services/FaceRecognitionService.cpp</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2804,12 +2804,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.cpp</t>
+          <t>src/services/FaceRecognitionService.h</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2819,12 +2819,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.h</t>
+          <t>src/services/MaintenanceService.cpp</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2834,12 +2834,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.cpp</t>
+          <t>src/services/MaintenanceService.h</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2849,12 +2849,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.h</t>
+          <t>src/services/ReturnService.cpp</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2864,12 +2864,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.cpp</t>
+          <t>src/services/ReturnService.h</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2879,12 +2879,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.h</t>
+          <t>src/services/SettingService.cpp</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2894,12 +2894,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.cpp</t>
+          <t>src/services/SettingService.h</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2909,12 +2909,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.h</t>
+          <t>src/services/ToolService.cpp</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2924,12 +2924,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>src/services/SettingService.cpp</t>
+          <t>src/services/ToolService.h</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2939,12 +2939,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>src/services/SettingService.h</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2954,12 +2954,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>src/services/ToolService.cpp</t>
+          <t>src/utils/DeviceProfile.h</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2969,7 +2969,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>src/services/ToolService.h</t>
+          <t>src/utils/PinyinDict.cpp</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>src/utils/StyleHelper.cpp</t>
+          <t>src/utils/PinyinDict.h</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2999,31 +2999,106 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>src/utils/PinyinDictData.h</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.h</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinPhraseData.h</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>src/utils/StyleHelper.cpp</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>src/utils/StyleHelper.h</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>808/833</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>41</v>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>800/830</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3037,7 +3112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3069,7 +3144,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3095,30 +3170,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/common/AppConfig.cpp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>loadAll</t>
+          <t>uiScale</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/common/AppConfig.cpp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>saveBatch</t>
+          <t>setUiScale</t>
         </is>
       </c>
     </row>
@@ -3129,63 +3204,63 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>loadAll</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.cpp</t>
+          <t>src/db/ConfigDAO.cpp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>28</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>onDownloadTemplate</t>
+          <t>saveBatch</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/db/ConfigDAO.cpp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>setupContent</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/BatchImportDialog.cpp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>255</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>buildPasswordRow</t>
+          <t>onDownloadTemplate</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/LedgerStatsPage.cpp</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3193,247 +3268,322 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>openKeypad</t>
+          <t>updateExportButtonSize</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/LedgerStatsPage.cpp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>onSubmit</t>
+          <t>resizeEvent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/RoleSelectDialog.cpp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>onExitLogin</t>
+          <t>setupContent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>332</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>setupContent</t>
+          <t>refresh</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>buildVerifyPage</t>
+          <t>applyScale</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>buildResetPage</t>
+          <t>detectScreenLogicalSize</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>buildPasswordRow</t>
+          <t>readConfigUiScale</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>openKeypad</t>
+          <t>logDeviceInfo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>206</v>
+        <v>13</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>showEvent</t>
+          <t>inputLetter</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hideEvent</t>
+          <t>backspace</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>onPollFace</t>
+          <t>clear</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>224</v>
+        <v>32</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>verifyOnce</t>
+          <t>setSurnameMode</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gotoResetPage</t>
+          <t>surnameMode</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>onResetSubmit</t>
+          <t>pageUp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>318</v>
+        <v>46</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>onCancel</t>
+          <t>pageDown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>setupContent</t>
+          <t>currentPage</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.cpp</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>330</v>
+        <v>57</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>refresh</t>
+          <t>pageCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>63</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>totalCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>67</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>candidatesForPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>78</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>85</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pinyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>89</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>buildFull</t>
         </is>
       </c>
     </row>

--- a/docs/代码体检报告.xlsx
+++ b/docs/代码体检报告.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21/22</t>
+          <t>19/20</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -529,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>44/46</t>
+          <t>36/38</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>15/20</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1159,37 +1159,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>int v =</t>
+          <t>21/21</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.cpp</t>
+          <t>src/components/SoftKeyboard.h</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23/23</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>src/components/SoftKeyboard.h</t>
+          <t>src/components/TopBar.cpp</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1199,12 +1199,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>src/components/TopBar.cpp</t>
+          <t>src/components/TopBar.h</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1214,12 +1214,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>src/components/TopBar.h</t>
+          <t>src/components/VerifyAlertDialog.cpp</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1229,12 +1229,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.cpp</t>
+          <t>src/components/VerifyAlertDialog.h</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1244,12 +1244,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>src/components/VerifyAlertDialog.h</t>
+          <t>src/controller/ToolController.cpp</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1259,12 +1259,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.cpp</t>
+          <t>src/controller/ToolController.h</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1274,12 +1274,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>src/controller/AuthController.h</t>
+          <t>src/controller/UserController.cpp</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1289,12 +1289,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.cpp</t>
+          <t>src/controller/UserController.h</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1304,12 +1304,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>src/controller/SettingController.h</t>
+          <t>src/db/AlertDAO.cpp</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1319,12 +1319,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.cpp</t>
+          <t>src/db/AlertDAO.h</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1334,7 +1334,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>src/controller/ToolController.h</t>
+          <t>src/db/BaseDAO.h</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>src/controller/UserController.cpp</t>
+          <t>src/db/DepartmentDAO.cpp</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1364,7 +1364,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>src/controller/UserController.h</t>
+          <t>src/db/DepartmentDAO.h</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1379,12 +1379,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.cpp</t>
+          <t>src/db/FaceRecogLogDAO.cpp</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1394,7 +1394,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>src/db/AlertDAO.h</t>
+          <t>src/db/FaceRecogLogDAO.h</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1409,12 +1409,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>src/db/BaseDAO.h</t>
+          <t>src/db/RecordDAO.cpp</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>17/17</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1424,12 +1424,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/db/RecordDAO.h</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1439,12 +1439,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.h</t>
+          <t>src/db/TaskTypeDAO.cpp</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1454,12 +1454,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.cpp</t>
+          <t>src/db/TaskTypeDAO.h</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1469,12 +1469,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>src/db/DepartmentDAO.h</t>
+          <t>src/db/ToolDAO.cpp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1484,12 +1484,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.cpp</t>
+          <t>src/db/ToolDAO.h</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1499,12 +1499,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>src/db/FaceRecogLogDAO.h</t>
+          <t>src/db/ToolDAOCategory.cpp</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1514,12 +1514,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.cpp</t>
+          <t>src/db/ToolDAOMachineGroup.cpp</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1529,12 +1529,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>src/db/RecordDAO.h</t>
+          <t>src/db/ToolDAOMaintenance.cpp</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1544,12 +1544,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.cpp</t>
+          <t>src/db/ToolDAOMapping.cpp</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1559,12 +1559,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>src/db/TaskTypeDAO.h</t>
+          <t>src/db/ToolDAOPosition.cpp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1574,12 +1574,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.cpp</t>
+          <t>src/db/ToolDAOToolEntity.cpp</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1589,12 +1589,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>src/db/ToolDAO.h</t>
+          <t>src/db/UserDAO.cpp</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1604,12 +1604,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOCategory.cpp</t>
+          <t>src/db/UserDAO.h</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1619,12 +1619,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMachineGroup.cpp</t>
+          <t>src/model/AlertLog.h</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1634,12 +1634,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMaintenance.cpp</t>
+          <t>src/model/BorrowRecord.h</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1649,12 +1649,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOMapping.cpp</t>
+          <t>src/model/TaskType.h</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1664,12 +1664,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOPosition.cpp</t>
+          <t>src/model/ToolCabinet.h</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1679,12 +1679,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>src/db/ToolDAOToolEntity.cpp</t>
+          <t>src/model/ToolCategory.h</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1694,12 +1694,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.cpp</t>
+          <t>src/model/ToolInfo.h</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>27/27</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1709,7 +1709,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>src/db/UserDAO.h</t>
+          <t>src/model/User.h</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1724,12 +1724,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>src/model/AlertLog.h</t>
+          <t>src/pages/AlertLogsPage.cpp</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1739,7 +1739,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>src/model/BorrowRecord.h</t>
+          <t>src/pages/AlertLogsPage.h</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>src/model/ReturnRecord.h</t>
+          <t>src/pages/AlertLogsPage.ui</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1763,18 +1763,18 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>src/model/TaskType.h</t>
+          <t>src/pages/BatchImportDialog.cpp</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1784,7 +1784,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>src/model/ToolCabinet.h</t>
+          <t>src/pages/BatchImportDialog.h</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1799,12 +1799,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>src/model/ToolCategory.h</t>
+          <t>src/pages/CabinetSessionDialog.cpp</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1814,7 +1814,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>src/model/ToolInfo.h</t>
+          <t>src/pages/CabinetSessionDialog.h</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1829,12 +1829,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>src/model/User.h</t>
+          <t>src/pages/ForceChangePasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1844,12 +1844,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.cpp</t>
+          <t>src/pages/ForceChangePasswordDialog.h</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1859,12 +1859,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.h</t>
+          <t>src/pages/ForgotPasswordDialog.cpp</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1874,7 +1874,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>src/pages/AlertLogsPage.ui</t>
+          <t>src/pages/ForgotPasswordDialog.h</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1883,18 +1883,18 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.cpp</t>
+          <t>src/pages/HelpManualDialog.cpp</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1904,7 +1904,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.h</t>
+          <t>src/pages/HelpManualDialog.h</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.cpp</t>
+          <t>src/pages/LedgerStatsPage.cpp</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1934,7 +1934,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>src/pages/CabinetSessionDialog.h</t>
+          <t>src/pages/LedgerStatsPage.h</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1949,27 +1949,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.cpp</t>
+          <t>src/pages/LedgerStatsPage.ui</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>src/pages/ForceChangePasswordDialog.h</t>
+          <t>src/pages/LoginPage.cpp</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>19/19</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1979,12 +1979,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.cpp</t>
+          <t>src/pages/LoginPage.h</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1994,12 +1994,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>src/pages/ForgotPasswordDialog.h</t>
+          <t>src/pages/LoginPageFace.cpp</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2009,12 +2009,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>src/pages/HelpManualDialog.cpp</t>
+          <t>src/pages/LoginPageUI.cpp</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2024,12 +2024,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>src/pages/HelpManualDialog.h</t>
+          <t>src/pages/MenuHomePage.cpp</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2039,12 +2039,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.cpp</t>
+          <t>src/pages/MenuHomePage.h</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2054,12 +2054,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.h</t>
+          <t>src/pages/RoleSelectDialog.cpp</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2069,7 +2069,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.ui</t>
+          <t>src/pages/RoleSelectDialog.h</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2078,18 +2078,18 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.cpp</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>21/23</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2099,7 +2099,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>src/pages/LoginPage.h</t>
+          <t>src/pages/SystemSettingsPage.h</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2114,12 +2114,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageFace.cpp</t>
+          <t>src/pages/SystemSettingsPageBackup.cpp</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2129,12 +2129,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>src/pages/LoginPageUI.cpp</t>
+          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2144,12 +2144,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>src/pages/MenuHomePage.cpp</t>
+          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2159,12 +2159,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>src/pages/MenuHomePage.h</t>
+          <t>src/pages/SystemSettingsPagePanels.cpp</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2174,12 +2174,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.cpp</t>
+          <t>src/pages/SystemSettingsPageTaskConfig.cpp</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2189,12 +2189,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.h</t>
+          <t>src/pages/ToolBorrowPage.cpp</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>17/17</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2204,12 +2204,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.cpp</t>
+          <t>src/pages/ToolBorrowPage.h</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21/22</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2219,7 +2219,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.h</t>
+          <t>src/pages/ToolBorrowPage.ui</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2228,18 +2228,18 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageBackup.cpp</t>
+          <t>src/pages/ToolBorrowPageFlow.cpp</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2249,12 +2249,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageDisplay.cpp</t>
+          <t>src/pages/ToolCheckinPage.cpp</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>38/38</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2264,12 +2264,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageNetwork.cpp</t>
+          <t>src/pages/ToolCheckinPage.h</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2279,27 +2279,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPagePanels.cpp</t>
+          <t>src/pages/ToolCheckinPage.ui</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPageTaskConfig.cpp</t>
+          <t>src/pages/ToolCheckinPageDialog.cpp</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2309,12 +2309,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.cpp</t>
+          <t>src/pages/ToolListDialog.cpp</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2324,7 +2324,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.h</t>
+          <t>src/pages/ToolListDialog.h</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2339,27 +2339,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPage.ui</t>
+          <t>src/pages/ToolManagementPage.cpp</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>src/pages/ToolBorrowPageFlow.cpp</t>
+          <t>src/pages/ToolManagementPage.h</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2369,27 +2369,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.cpp</t>
+          <t>src/pages/ToolManagementPage.ui</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.h</t>
+          <t>src/pages/ToolManagementPageDetail.cpp</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2399,27 +2399,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPage.ui</t>
+          <t>src/pages/ToolManagementPageDocument.cpp</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>src/pages/ToolCheckinPageDialog.cpp</t>
+          <t>src/pages/ToolManagementPageToolForm.cpp</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2429,12 +2429,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>src/pages/ToolListDialog.cpp</t>
+          <t>src/pages/ToolReturnPage.cpp</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2444,7 +2444,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>src/pages/ToolListDialog.h</t>
+          <t>src/pages/ToolReturnPage.h</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2459,27 +2459,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.cpp</t>
+          <t>src/pages/ToolReturnPage.ui</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.h</t>
+          <t>src/pages/UserManagementPage.cpp</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2489,7 +2489,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPage.ui</t>
+          <t>src/pages/UserManagementPage.h</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2498,33 +2498,33 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDetail.cpp</t>
+          <t>src/pages/UserManagementPage.ui</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageDocument.cpp</t>
+          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2534,12 +2534,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>src/pages/ToolManagementPageToolForm.cpp</t>
+          <t>src/pages/UserManagementPageUserDialog.cpp</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2549,12 +2549,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.cpp</t>
+          <t>src/services/AlertService.cpp</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2564,7 +2564,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.h</t>
+          <t>src/services/AlertService.h</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2579,27 +2579,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>src/pages/ToolReturnPage.ui</t>
+          <t>src/services/AuthService.cpp</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>14/14</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.cpp</t>
+          <t>src/services/AuthService.h</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2609,12 +2609,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.h</t>
+          <t>src/services/BorrowService.cpp</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2624,7 +2624,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPage.ui</t>
+          <t>src/services/BorrowService.h</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2633,18 +2633,18 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageFaceEnroll.cpp</t>
+          <t>src/services/CheckoutService.cpp</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2654,12 +2654,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>src/pages/UserManagementPageUserDialog.cpp</t>
+          <t>src/services/CheckoutService.h</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2669,12 +2669,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>src/services/AlertService.cpp</t>
+          <t>src/services/FaceRecognitionService.cpp</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2684,7 +2684,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>src/services/AlertService.h</t>
+          <t>src/services/FaceRecognitionService.h</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2699,12 +2699,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>src/services/AuthService.cpp</t>
+          <t>src/services/MaintenanceService.cpp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>16/16</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2714,7 +2714,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>src/services/AuthService.h</t>
+          <t>src/services/MaintenanceService.h</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2729,12 +2729,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.cpp</t>
+          <t>src/services/ReturnService.cpp</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2744,7 +2744,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>src/services/BorrowService.h</t>
+          <t>src/services/ReturnService.h</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2759,12 +2759,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.cpp</t>
+          <t>src/services/SettingService.cpp</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2774,7 +2774,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>src/services/CheckoutService.h</t>
+          <t>src/services/SettingService.h</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2789,12 +2789,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.cpp</t>
+          <t>src/services/ToolService.cpp</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2804,7 +2804,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>src/services/FaceRecognitionService.h</t>
+          <t>src/services/ToolService.h</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2819,12 +2819,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2834,7 +2834,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>src/services/MaintenanceService.h</t>
+          <t>src/utils/DeviceProfile.h</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2849,12 +2849,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.cpp</t>
+          <t>src/utils/PinyinDict.cpp</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2864,7 +2864,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>src/services/ReturnService.h</t>
+          <t>src/utils/PinyinDict.h</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>src/services/SettingService.cpp</t>
+          <t>src/utils/PinyinDictData.h</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2894,12 +2894,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>src/services/SettingService.h</t>
+          <t>src/utils/PinyinInput.cpp</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/14</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2909,12 +2909,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>src/services/ToolService.cpp</t>
+          <t>src/utils/PinyinInput.h</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2924,7 +2924,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>src/services/ToolService.h</t>
+          <t>src/utils/PinyinPhraseData.h</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2939,12 +2939,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>src/utils/DeviceProfile.cpp</t>
+          <t>src/utils/ScreenFit.h</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2954,7 +2954,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>src/utils/DeviceProfile.h</t>
+          <t>src/utils/StyleHelper.cpp</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>src/utils/PinyinDict.cpp</t>
+          <t>src/utils/StyleHelper.h</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2981,124 +2981,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>src/utils/PinyinDict.h</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>src/utils/PinyinDictData.h</t>
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>728/760</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>src/utils/PinyinInput.cpp</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>0/14</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>src/utils/PinyinInput.h</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>src/utils/PinyinPhraseData.h</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>src/utils/StyleHelper.cpp</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>src/utils/StyleHelper.h</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>800/830</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3112,7 +3007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3144,7 +3039,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>843</v>
+        <v>923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3174,11 +3069,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>uiScale</t>
+          <t>lastBackupDate</t>
         </is>
       </c>
     </row>
@@ -3189,161 +3084,161 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>327</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>setUiScale</t>
+          <t>setLastBackupDate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>loadAll</t>
+          <t>hasCamera</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>saveBatch</t>
+          <t>availableCameras</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>src/db/ConfigDAO.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>start</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>src/pages/BatchImportDialog.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>onDownloadTemplate</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.cpp</t>
+          <t>src/components/CameraCapture.cpp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>updateExportButtonSize</t>
+          <t>onCaptureTimer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>src/pages/LedgerStatsPage.cpp</t>
+          <t>src/controller/ToolController.cpp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>resizeEvent</t>
+          <t>addToolWithPosition</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>src/pages/RoleSelectDialog.cpp</t>
+          <t>src/controller/ToolController.cpp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>setupContent</t>
+          <t>resolveCabinetId</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>src/pages/SystemSettingsPage.cpp</t>
+          <t>src/db/ToolDAOMapping.cpp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>332</v>
+        <v>88</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>refresh</t>
+          <t>findCabinetIdByPrefix</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>src/utils/DeviceProfile.cpp</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>applyScale</t>
+          <t>initBackupScheduler</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>src/utils/DeviceProfile.cpp</t>
+          <t>src/pages/SystemSettingsPage.cpp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>detectScreenLogicalSize</t>
+          <t>onBackupTimerTick</t>
         </is>
       </c>
     </row>
@@ -3354,11 +3249,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>readConfigUiScale</t>
+          <t>applyScale</t>
         </is>
       </c>
     </row>
@@ -3369,41 +3264,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>logDeviceInfo</t>
+          <t>detectScreenLogicalSize</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>src/utils/PinyinInput.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inputLetter</t>
+          <t>readConfigUiScale</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>src/utils/PinyinInput.cpp</t>
+          <t>src/utils/DeviceProfile.cpp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>backspace</t>
+          <t>logDeviceInfo</t>
         </is>
       </c>
     </row>
@@ -3414,11 +3309,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>inputLetter</t>
         </is>
       </c>
     </row>
@@ -3429,11 +3324,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>setSurnameMode</t>
+          <t>backspace</t>
         </is>
       </c>
     </row>
@@ -3444,11 +3339,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>surnameMode</t>
+          <t>clear</t>
         </is>
       </c>
     </row>
@@ -3459,11 +3354,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pageUp</t>
+          <t>setSurnameMode</t>
         </is>
       </c>
     </row>
@@ -3474,11 +3369,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pageDown</t>
+          <t>surnameMode</t>
         </is>
       </c>
     </row>
@@ -3489,11 +3384,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>currentPage</t>
+          <t>pageUp</t>
         </is>
       </c>
     </row>
@@ -3504,11 +3399,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pageCount</t>
+          <t>pageDown</t>
         </is>
       </c>
     </row>
@@ -3519,11 +3414,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>totalCount</t>
+          <t>currentPage</t>
         </is>
       </c>
     </row>
@@ -3534,11 +3429,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>candidatesForPage</t>
+          <t>pageCount</t>
         </is>
       </c>
     </row>
@@ -3549,11 +3444,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>totalCount</t>
         </is>
       </c>
     </row>
@@ -3564,11 +3459,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pinyin</t>
+          <t>candidatesForPage</t>
         </is>
       </c>
     </row>
@@ -3579,9 +3474,39 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>78</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>85</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>pinyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>src/utils/PinyinInput.cpp</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>89</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>buildFull</t>
         </is>
@@ -3598,7 +3523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3620,6 +3545,51 @@
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeService.cpp</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>270</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>// 安全闸门：周期帧上报的 8 路摄像头任一异常则禁止开柜（货位识别可信度下降，袁总安全策略）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>src/comm/EdgeService.h</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>* @note  摄像头异常属安全红线：货位识别可信度下降，禁止开锁（袁总安全策略）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>src/common/Constants.h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>// 使用方：FaceRecognitionService（识别判定写入）、LoginPage::faceResultN</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3666,7 +3636,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3682,7 +3652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3698,7 +3668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3710,11 +3680,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>src/comm/EdgeService.cpp</t>
+          <t>src/comm/EdgeService.h</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>361</v>
+        <v>149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3726,11 +3696,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>src/comm/EdgeService.h</t>
+          <t>src/common/UserInputValidator.h</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3738,22 +3708,6 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>src/common/UserInputValidator.h</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>79</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>文件末尾缺换行</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
